--- a/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
+++ b/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
+++ b/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
+++ b/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
+++ b/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
+++ b/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
+++ b/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
+++ b/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
+++ b/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
+++ b/StructureDefinition-SEEHDSAllergyIntolerance.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2161" uniqueCount="436">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1109,6 +1109,42 @@
   </si>
   <si>
     <t>Datum för konstaterande (alertInformationBody.ascertainedDate)</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.onset[x]:onsetAge</t>
+  </si>
+  <si>
+    <t>onsetAge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age
+</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.onset[x]:onsetPeriod</t>
+  </si>
+  <si>
+    <t>onsetPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.onset[x]:onsetRange</t>
+  </si>
+  <si>
+    <t>onsetRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.onset[x]:onsetString</t>
+  </si>
+  <si>
+    <t>onsetString</t>
   </si>
   <si>
     <t>AllergyIntolerance.recordedDate</t>
@@ -1689,7 +1725,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.0234375" customWidth="true" bestFit="true"/>
@@ -6271,14 +6307,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>340</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>79</v>
       </c>
@@ -6290,7 +6328,7 @@
         <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>79</v>
@@ -6299,13 +6337,13 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>219</v>
+        <v>342</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6356,7 +6394,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6371,25 +6409,27 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="B43" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="C43" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>347</v>
+        <v>79</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6399,7 +6439,7 @@
         <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>79</v>
@@ -6408,13 +6448,13 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6465,7 +6505,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6480,25 +6520,27 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="D44" t="s" s="2">
-        <v>354</v>
+        <v>79</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6508,26 +6550,24 @@
         <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>348</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6576,7 +6616,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6591,23 +6631,25 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>360</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>79</v>
       </c>
@@ -6628,17 +6670,15 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>219</v>
+        <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>362</v>
+        <v>332</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -6687,7 +6727,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>361</v>
+        <v>331</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6702,10 +6742,10 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>365</v>
+        <v>335</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>79</v>
+        <v>336</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -6713,10 +6753,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6727,7 +6767,7 @@
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>88</v>
@@ -6739,17 +6779,15 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>367</v>
+        <v>219</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -6798,13 +6836,13 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
@@ -6813,32 +6851,32 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>79</v>
+        <v>358</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>88</v>
@@ -6850,13 +6888,13 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6907,13 +6945,13 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
@@ -6922,25 +6960,25 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>79</v>
+        <v>365</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6950,24 +6988,26 @@
         <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>101</v>
+        <v>359</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>102</v>
+        <v>366</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7016,7 +7056,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>104</v>
+        <v>364</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7028,35 +7068,35 @@
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>105</v>
+        <v>369</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>79</v>
@@ -7068,16 +7108,16 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>109</v>
+        <v>373</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>110</v>
+        <v>374</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>111</v>
+        <v>375</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7127,22 +7167,22 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>115</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>105</v>
+        <v>376</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>79</v>
@@ -7151,16 +7191,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>380</v>
+        <v>79</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7170,29 +7210,27 @@
         <v>78</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>108</v>
+        <v>378</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
       </c>
@@ -7240,7 +7278,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7252,10 +7290,10 @@
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>186</v>
+        <v>382</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>79</v>
@@ -7266,10 +7304,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7280,7 +7318,7 @@
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>88</v>
@@ -7292,7 +7330,7 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>236</v>
+        <v>384</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>385</v>
@@ -7300,9 +7338,7 @@
       <c r="M51" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="N51" t="s" s="2">
-        <v>387</v>
-      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -7327,11 +7363,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>388</v>
+        <v>79</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -7349,13 +7387,13 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
@@ -7364,7 +7402,7 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>79</v>
@@ -7375,21 +7413,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>391</v>
+        <v>79</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -7401,17 +7439,15 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>236</v>
+        <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>392</v>
+        <v>102</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7436,13 +7472,13 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -7460,47 +7496,47 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>390</v>
+        <v>104</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>259</v>
+        <v>105</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>397</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>399</v>
+        <v>107</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -7512,16 +7548,16 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>400</v>
+        <v>109</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>401</v>
+        <v>110</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>402</v>
+        <v>111</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7571,22 +7607,22 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>398</v>
+        <v>115</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>403</v>
+        <v>105</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>79</v>
@@ -7597,42 +7633,46 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>219</v>
+        <v>108</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
       </c>
@@ -7680,36 +7720,36 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>335</v>
+        <v>186</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>407</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7732,16 +7772,16 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>163</v>
+        <v>236</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7767,13 +7807,11 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -7791,7 +7829,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7806,7 +7844,7 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>278</v>
+        <v>400</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>79</v>
@@ -7817,21 +7855,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>79</v>
+        <v>402</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -7846,13 +7884,13 @@
         <v>236</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7878,13 +7916,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -7902,13 +7940,13 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
@@ -7917,32 +7955,32 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>420</v>
+        <v>259</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>79</v>
+        <v>408</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -7954,16 +7992,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>367</v>
+        <v>101</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8013,13 +8051,13 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
@@ -8028,17 +8066,459 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>371</v>
+        <v>414</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM57">
+  <autoFilter ref="A1:AM61">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8048,7 +8528,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI56">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
